--- a/test/QA_test_with_chatbot_responses.xlsx
+++ b/test/QA_test_with_chatbot_responses.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,10 +451,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>error</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>test_session_id</t>
         </is>
@@ -471,24 +476,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The MPA program at SPAA values personal statements that clearly articulate your academic background, professional experiences, and alignment with the program’s mission to prepare leaders in public service. While the specific criteria for evaluation are not detailed in our retrieved documents, personal statements are typically assessed for their ability to:  
-- Demonstrate your understanding of public administration principles and their relevance to your career goals [link](https://spaa.newark.rutgers.edu/mpa).  
-- Highlight how your unique experiences (e.g., internships, research, or community work) connect to the program’s focus on leadership, ethics, and evidence-based decision-making [link](https://spaa.newark.rutgers.edu/online-mpa).  
-- Show your readiness to engage with the program’s curriculum, including its capstone project and elective specializations [link](https://spaa.newark.rutgers.edu/mpa).  
+          <t>The SPAA MPA program seeks personal statements that reflect your academic background, professional experiences, and alignment with the program’s mission to prepare leaders in public service. While the specific criteria aren’t detailed in the retrieved documents, a strong statement typically includes:  
+- **Clear purpose**: Explain why you’re pursuing an MPA and how it connects to your career goals (e.g., public management, nonprofit leadership, or policy analysis).  
+- **Relevant experiences**: Highlight coursework, internships, or projects demonstrating your interest in public affairs, leadership, or community engagement.  
+- **Program fit**: Mention specific SPAA resources (e.g., faculty expertise, tracks, or certificates) that align with your aspirations.  
+**Recommended structure**: Begin with a concise introduction about your background, followed by a narrative of experiences that shaped your interest in public service, and conclude with how the MPA will help you achieve your goals.  
 **Common mistakes to avoid**:  
-- Being overly generic or vague about your goals.  
-- Failing to connect your background to the program’s values (e.g., public service, equity, or innovation).  
-- Overlooking the importance of clarity and conciseness.  
-For tailored guidance, we recommend reaching out to **Aaron Gibbs**, the MPA admissions contact, at *aaron.gibbs@newark.rutgers.edu* [link](https://spaa.newark.rutgers.edu/how-apply-mpa). They can provide insights specific to SPAA’s expectations. Good luck!</t>
+- Being overly generic (e.g., “I want to help people” without specific examples).  
+- Focusing too much on personal achievements without linking them to public service.  
+- Neglecting to address how the MPA’s curriculum or tracks align with your career path.  
+For more details, visit our [MPA program page](https://spaa.newark.rutgers.edu/mpa).</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>batch_test_19d81ff4c8cb</t>
+        <v>21.62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>batch_test_a770141b9115437ea89fb17b7fa19325</t>
         </is>
       </c>
     </row>
@@ -503,19 +512,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>It's great to see your work in the nonprofit sector. Your background in nonprofits and private companies is a strength, as SPAA values diverse experiences and how they align with public service goals. Admissions are reviewed holistically, so your professional experience—especially in areas like leadership, resource development, or program management—can strengthen your application.  
-When crafting your application, emphasize how your nonprofit and private-sector work has shaped your understanding of public impact, equity, or organizational challenges. For example, if you’ve managed grants, led teams, or navigated complex systems, connect these skills to SPAA’s focus areas like nonprofit leadership, policy, or community engagement. The **Nonprofit Management Certificate** or **MPA nonprofit track** could also align with your goals, as they offer specialized training in areas like grant writing, financial management, and strategic planning [link](https://spaa.newark.rutgers.edu/nonprofit-management-certificate).  
-If you’re applying for the MPA, highlight how your background prepares you to contribute to SPAA’s mission of advancing public service. For instance, your private-sector experience might offer unique insights into cross-sector collaboration, while nonprofit work demonstrates your commitment to mission-driven work. Let your application showcase how your journey bridges these sectors to create meaningful change.  
-For further guidance, reach out to **Aaron Gibbs** for details on the Nonprofit Management Certificate or MPA program structure [link](https://spaa.newark.rutgers.edu/nonprofit-management-certificate). Your diverse perspective is an asset!</t>
+          <t>It's great to connect with someone working in a nonprofit organization. It's great to connect with someone working in a nonprofit organization! Your background in nonprofits and private companies is actually a strong asset for the MPA program. SPAA values diverse experiences and seeks candidates who can contribute unique perspectives to our community.  
+For the **Nonprofit Management track**, your experience aligns well with the program’s focus on leadership, financial management, and grant writing—key areas covered in required courses like *Principles of Nonprofit Leadership and Management* and *Nonprofit Budgeting and Financial Management*. You can emphasize how your work in nonprofits has shaped your understanding of organizational governance, stakeholder engagement, or program evaluation. Similarly, private sector experience can highlight skills in strategic planning, project management, or innovation, which are relevant to both tracks.  
+When applying, focus on how your background prepares you to tackle real-world challenges in public service. The capstone project allows you to connect your experience with a research paper or portfolio, so highlight specific projects or roles that demonstrate your impact. SPAA’s flexible curriculum also lets you tailor electives to deepen expertise in areas like nonprofit management or public policy.  
+Your non-government experience isn’t a disadvantage—it’s an opportunity to bring fresh insights to the program. Good luck! 🌟</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.91</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>batch_test_d6f9ae5a3273</t>
+        <v>22.15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>batch_test_cdf811b6cecc40b0b4be49afa964b535</t>
         </is>
       </c>
     </row>
@@ -530,18 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>If you’ve already submitted your application but want to share your promotion, you can’t directly update the submitted materials. However, you can contact the admissions team to provide additional context about your recent promotion. This may help clarify your qualifications, though it’s not a formal update to the application itself.  
-For questions about your application or to share updates, reach out to **Aaron Gibbs**, Associate Dean of Student and Academic Services, at *algibbs@rutgers.edu* [link](https://spaa.newark.rutgers.edu/how-apply-empa). They can guide you on next steps or whether further details might be considered.  
-If you’re applying to a program like the EMPA, PhD, or MPA, note that fee waivers or deferrals are available for scholars, veterans, or under extraordinary circumstances [link](https://spaa.newark.rutgers.edu/how-apply-certificates). Let me know if you’d like help exploring these options!</t>
+          <t>You can update your application by submitting a revised resume through the application portal. The SPAA allows applicants to revise their materials after submission, particularly for significant updates like a promotion [link](https://spaa.newark.rutgers.edu/apply). Ensure your resume highlights the new role and its relevance to your academic or career goals. If you need further guidance, our team is here to help!</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>batch_test_35de670cb1e4</t>
+        <v>17.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>batch_test_0c37f920a57442148a4e8c0e1a4a88f9</t>
         </is>
       </c>
     </row>
@@ -556,21 +569,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Our advisors evaluate transfer credits on a case-by-case basis, focusing on course alignment with SPAA’s program goals and academic rigor. For graduate-level coursework from institutions outside New Jersey (like your college in Mexico), the evaluation process considers:  
-1. **Relevance to SPAA’s curriculum**: Courses must closely match SPAA’s core areas (e.g., public policy, nonprofit management, governance) and align with your program of study (e.g., MPA or certificate tracks).  
-2. **Credit equivalency**: SPAA’s faculty review course descriptions, syllabi, and grading to ensure the work meets Rutgers’ academic standards.  
-3. **Program-specific policies**: For graduate credits, SPAA’s MPA program allows up to 12 transfer credits from related graduate fields, provided they were completed within the last 10 years and with a grade of B or better [link](https://spaa.newark.rutgers.edu/degree-completion-individualized-dual-degree-mpa).  
-Since your coursework is from an international institution, we recommend reaching out to **Aaron Gibbs**, associate dean for student services, at *algibbs@rutgers.edu* for personalized guidance. He can help clarify how your credits might apply to your program and next steps for formal evaluation.  
-If you’re pursuing the Budgeting and Financial Management Certificate, note that three graduate courses from SPAA’s approved list can also be transferred, though this is separate from degree credit evaluation [link](https://spaa.newark.rutgers.edu/budgeting-and-financial-management-certificate). Let me know if you’d like help identifying relevant courses!</t>
+          <t>SPAA evaluates transfer credits on a case-by-case basis, focusing on course equivalency, accreditation, and alignment with program requirements. For graduate-level courses taken abroad, the following factors typically determine acceptance:  
+- **Accreditation**: Courses must come from a regionally accredited institution.  
+- **Relevance**: Credits should align with SPAA’s curriculum (e.g., public policy, administration, or related fields).  
+- **Equivalency**: Courses must match SPAA’s degree requirements in content and credit hours.  
+- **Transcript Evaluation**: Official transcripts and course descriptions are reviewed to assess suitability.  
+Since your courses were taken at a Mexican institution, we recommend contacting **Aaron Gibbs**, associate dean of student and academic services, for detailed guidance on your specific situation. He can help clarify how your credits might apply to SPAA programs [link](https://spaa.newark.rutgers.edu/undergraduate-transfer-students-outside-rutgers).  
+For prospective students, SPAA’s programs emphasize practical skills in public administration, nonprofit management, and policy analysis—preparing graduates for impactful careers in government, NGOs, and more. If you’re considering applying, our admissions team is here to help you explore how your academic background fits with our programs!</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.77</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>batch_test_246b1cf84953</t>
+        <v>21.38</v>
+      </c>
+      <c r="E5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>batch_test_fae44ff808bf4075b5df5f8271aa0776</t>
         </is>
       </c>
     </row>
@@ -585,18 +602,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>If you're working full-time while enrolled in the MPA program, the curriculum is designed with flexibility in mind to accommodate professional commitments. The core courses (7 courses / 21 credits) and elective courses (6 courses / 18 credits) are structured to allow students to balance academic and work responsibilities, with many courses available online [link](https://spaa.newark.rutgers.edu/online-mpa). If you find the initial months challenging, it’s important to communicate with your academic advisor early—they can help you adjust your course load or explore options like delaying certain courses to ensure you maintain a manageable workload.  
-While the program does not explicitly outline formal options to "pause" studies, students are encouraged to work closely with the SPAA program office to create a personalized academic plan. For example, you might adjust your elective choices or delay the capstone project to align with your professional schedule. The program’s flexibility in electives and tracks [link](https://spaa.newark.rutgers.edu/mpa) allows for tailored pathways that can adapt to changing circumstances.  
-If you’re unsure how to proceed, reach out to **Aaron Gibbs**, associate dean of student and academic services, at *algibbs@rutgers.edu* for guidance. They can help you navigate adjustments while ensuring you stay on track to graduate.</t>
+          <t>If you're planning to work full-time while enrolled in the MPA program, flexibility is a key strength of our program. The MPA curriculum is designed to accommodate working professionals, with part-time enrollment options allowing you to balance your career and studies [link](https://spaa.newark.rutgers.edu/mpa). You’ll take 7 core courses (21 credits) and 6 electives (18 credits), plus a capstone project (3 credits), but you can spread these across semesters to align with your workload.  
+If you find the initial months challenging, you can adjust your course load by taking fewer courses per semester. While the program doesn’t offer an official “pause” option, part-time enrollment allows you to reduce your academic commitment without leaving the program. For personalized guidance, our academic advisors can help you tailor your schedule to your professional and personal priorities.  
+For working professionals, our online MPA option provides asynchronous access to coursework, further supporting flexibility [link](https://spaa.newark.rutgers.edu/online-mpa). If you’re unsure about your ability to manage the workload, reaching out to an advisor early can help you create a realistic plan.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.61</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>batch_test_d938c14f3b69</t>
+        <v>30.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>batch_test_19089a144d8443b0ba6775c8d7b8d04a</t>
         </is>
       </c>
     </row>
@@ -611,19 +631,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Acknowledgment:  
-Our MPA program offers a range of funding opportunities to support students’ academic and professional growth. While we don’t publicly list individual student success stories due to privacy considerations, we encourage you to explore the **Academic Excellence Fund**, **Diversity Fund for graduate students**, and **Marc Holzer Fund for doctoral students**—these initiatives provide financial aid, scholarships, and support for internships and leadership development [link](https://spaa.newark.rutgers.edu/giving).  
-For personalized guidance on funding options, including assistantships or external grants, I recommend reaching out to **Aaron Gibbs, Associate Dean of Student and Academic Services** at *algibbs@rutgers.edu*. They can help tailor your search based on your background and goals.  
-Additionally, our financial aid office can provide details on federal and state aid programs, work-study opportunities, and other resources to make your MPA journey more affordable. Let me know if you’d like assistance connecting with them!</t>
+          <t>The MPA program offers various funding opportunities, including federal and institutional grants, scholarships, and tuition assistance programs. While specific examples of past recipients aren’t listed in our records, many students have successfully secured external funding through organizations focused on public service, nonprofit leadership, or policy research. For instance, some MPA students have received support from foundations like the Robert Wood Johnson Foundation or the Joyce Foundation, though individual eligibility depends on alignment with their career goals and academic focus.  
+To explore options, you might review the [financial aid section of our website](https://spaa.newark.rutgers.edu/financial-assistance) for details on available scholarships and application processes. Additionally, the [2022-2023 MPA Capstone Portfolios](https://spaa.newark.rutgers.edu/2022-2023-mpa-capstone-portfolios) and [2023-2024 MPA Capstone Portfolios](https://spaa.newark.rutgers.edu/2023-2024-mpa-capstone-portfolios) pages highlight student projects that often reflect grant-funded research or community initiatives, which could inspire your own funding strategies.  
+For personalized guidance on funding opportunities, consider reaching out to the SPAA financial aid office during their designated hours.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>batch_test_567ba2bd767b</t>
+        <v>22.28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>batch_test_bf0b7a622b2e44d79069b691b423f3ec</t>
         </is>
       </c>
     </row>
@@ -638,22 +660,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>We appreciate your work in public safety. The **Master of Public Administration (MPA)** program at SPAA is designed to equip professionals like yourself with the leadership and management skills needed for advanced roles in public service. Here’s how it can support your career transition:  
-1. **Leadership Focus**: The curriculum emphasizes leadership development, evidence-based decision-making, and managing diverse teams—critical for supervisory roles. Courses in public policy, organizational behavior, and ethics prepare you to address complex challenges in law enforcement and public administration [link](https://spaa.newark.rutgers.edu/mpa).  
-2. **Customizable Tracks**: Choose the **Public Management** track to align with your goals, focusing on governance, resource allocation, and policy implementation. This track is ideal for advancing into leadership within governmental or public safety organizations [link](https://spaa.newark.rutgers.edu/mpa).  
-3. **Online Flexibility**: The **Online MPA** option allows you to balance your career while earning your degree. The asynchronous format is tailored for working professionals seeking to enhance their skills without interrupting their duties [link](https://spaa.newark.rutgers.edu/online-mpa).  
-4. **Capstone Projects**: Apply your learning through a capstone project that tackles real-world issues in public service. Past projects include evaluations of leadership programs and policy analyses, offering hands-on experience that strengthens your resume [link](https://spaa.newark.rutgers.edu/mpa-capstone-portfolios).  
-5. **Specialized Certifications**: Pursue certificates like **Leadership of Public Organizations** to deepen expertise in management strategies, further distinguishing your qualifications for supervisory roles [link](https://spaa.newark.rutgers.edu/mpa).  
-For more details, visit our program page or reach out to our admissions team. We’re here to help you navigate this next step in your career!</t>
+          <t>Thank you for your public service. As a police officer aiming for leadership or supervisory roles, the **Master of Public Administration (MPA)** program at SPAA can provide valuable skills in public management, policy analysis, and organizational leadership—critical for advancing in public service.  
+The MPA curriculum emphasizes **leadership and management**, preparing students to address complex challenges in government and nonprofit sectors. For example, core courses like *Public Management Track* and *Nonprofit Management Track* allow you to tailor your studies to your career goals, while electives in areas like **government technology** or **performance measurement** can enhance your strategic thinking and operational expertise [link](https://spaa.newark.rutgers.edu/advance-to-grad).  
+Additionally, the program’s **capstone project** lets you apply classroom learning to real-world issues, such as designing policies or improving organizational efficiency—exactly the kind of practical experience that can set you apart in leadership roles. If you’re already a Rutgers-Newark undergraduate, the **Advance-to-Grad initiative** offers a streamlined path to the MPA without traditional application hurdles [link](https://spaa.newark.rutgers.edu/advance-to-grad).  
+For working professionals, the **online MPA option** provides flexibility to balance your career while advancing your education. Whether you’re aiming for supervisory roles or broader administrative responsibilities, the MPA equips you with the tools to lead effectively in public service.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>batch_test_622d31a12cf7</t>
+        <v>22.68</v>
+      </c>
+      <c r="E8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>batch_test_df713d0b43db46059d61f8c0f362181d</t>
         </is>
       </c>
     </row>
@@ -668,20 +690,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SPAA’s MPA program stands out in New Jersey through several unique features. For instance, our **Advance-to-Grad initiative** allows high-achieving Rutgers-Newark undergraduates to seamlessly transition to the MPA program without traditional application hurdles, waiving fees, letters of recommendation, and test scores [link](https://spaa.newark.rutgers.edu/advance-to-grad). This streamlined pathway is exclusive to SPAA and benefits students aiming to accelerate their academic and career goals.  
-Additionally, SPAA offers the **Accelerated MPA Dual Degree (BA/MPA or BS/MPA)**, enabling undergraduates to earn both degrees in five years by taking up to 18 graduate-level MPA credits as undergraduates [link](https://spaa.newark.rutgers.edu/accelerated-mpa). This dual-degree structure is tailored for students seeking to integrate public administration into their undergraduate curriculum, with flexible tracks and reduced time-to-degree.  
-Our **Degree Completion and Individualized Dual-Degree Options** also differentiate SPAA, allowing students to transfer up to 12 graduate credits from related fields toward the MPA, ideal for those with prior graduate education in areas like public health, law, or urban affairs [link](https://spaa.newark.rutgers.edu/degree-completion-individualized-dual-degree-mpa). This flexibility reduces the total credits needed to complete the MPA, making it accessible to a broader audience.  
-Finally, SPAA’s **JD/MPA joint program** with Rutgers School of Law-Newark is a rare opportunity to earn both degrees in four years, combining legal and public administration expertise [link](https://spaa.newark.rutgers.edu/jd-mpa). These distinctive pathways, along with our strong emphasis on practical skills and community engagement, position SPAA as a leader in public affairs education.  
-For more details, reach out to **Aaron Gibbs**, associate dean of student and academic services, at *algibbs@rutgers.edu*.</t>
+          <t>SPAA’s MPA program stands out in New Jersey through several unique features. One key distinction is the **Advance-to-Grad initiative**, which allows high-achieving Rutgers-Newark undergraduates to seamlessly transition into the MPA program without traditional application requirements, waiving fees, letters of recommendation, and standardized test scores [S2]. This streamlined pathway is exclusive to RU-N graduates.  
+Another differentiator is the **Accelerated MPA Dual Degree (BA/MPA or BS/MPA)**, enabling undergraduates to earn both degrees in five years by taking 18 graduate-level MPA credits as part of their undergraduate curriculum [S3]. This dual-degree structure is tailored for students seeking advanced preparation in public administration alongside their bachelor’s degree.  
+SPAA also offers the **JD/MPA joint degree program**, a rare four-year pathway combining law and public administration, allowing students to earn both degrees efficiently through collaboration with Rutgers School of Law-Newark [S4]. Additionally, the **State of NJ Certified Public Manager® (CPM) program** provides a state-accredited certificate that can transfer up to 15 undergraduate credits or 9 graduate credits toward an MPA degree, offering a flexible route for working professionals [S10].  
+These options, along with SPAA’s emphasis on practical training and customizable tracks, position it as a distinctive choice for students aiming to blend academic rigor with real-world public sector preparation.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>batch_test_c92a91c24759</t>
+        <v>25.65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>batch_test_627d93f52c08402780a38f7ff2c00bf0</t>
         </is>
       </c>
     </row>
@@ -696,18 +720,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>It’s absolutely fine to reach out directly to SPAA staff or faculty—they’re here to help! For admissions, funding, and course planning, we recommend starting with the **Admissions Office** for personalized guidance. They can assist with application timelines, financial aid options, and academic planning tailored to your goals. You can contact them at *admissions@newark.rutgers.edu* or visit our admissions page for more details [link](https://spaa.newark.rutgers.edu/application-for-tranfer-credit).  
-For course planning, academic advisors in the SPAA program can help you map out your curriculum, especially if you’re unsure about prerequisites or electives. Many students find it helpful to connect with faculty or current students during orientation or via the program’s advising portal.  
-If funding is a concern, the SPAA offers scholarships to MPA students after completing 9 credits, and financial aid advisors can guide you through grants, loans, and other resources. Don’t hesitate to ask—our team is committed to ensuring you have the tools to succeed!</t>
+          <t>For admissions, funding, and course planning, contacting SPAA’s admissions office directly is a great way to get personalized guidance. You can reach out through our website [link](https://spaa.newark.rutgers.edu/apply) for details on application deadlines, program-specific requirements, and support for prospective students.  
+For funding, SPAA offers scholarships to MPA students after completing 9 credits, and veteran students may qualify for specialized support services [link](https://spaa.newark.rutgers.edu/apply). For course planning, our BA program includes foundational courses like *Understanding Public Administration and the Public Sector* (40:834:200) and *Career Explorations in Public Service* (40:834:429), which provide essential skills for career development [link](https://spaa.newark.rutgers.edu/academics/courses/understanding-public-administration-and-public-sector).  
+If you need further assistance, our admissions team can help tailor your academic and financial plan. Let me know how I can support your journey!</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>batch_test_a5939c60c89a</t>
+        <v>24.65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>batch_test_653ccb60b4aa493998a58359589f8d49</t>
         </is>
       </c>
     </row>
@@ -722,18 +749,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thank you for your service. The SPAA MPA program is well-suited for veterans like you, as it emphasizes leadership, public service, and real-world problem-solving—skills honed through military experience. Our program offers **customizable tracks** in Public Management or Nonprofit Management, allowing you to tailor your studies to your career goals in civilian public service [link](https://spaa.newark.rutgers.edu/mpa).  
-We also provide dedicated support for military-connected students, including **Veteran Enrollment Certification** and access to financial aid options like the Post-9/11 GI Bill to help offset costs [link](https://spaa.newark.rutgers.edu/military-connected-students). The **capstone project** is another strength, letting you apply your expertise to community impact initiatives or policy challenges—perfect for translating your leadership experience into actionable outcomes [link](https://spaa.newark.rutgers.edu/2023-2024-mpa-capstone-portfolios).  
-If you’d like guidance on admissions or program specifics, **Aaron Gibbs**, our associate dean of student and academic services, is available to assist: *email: algibbs@rutgers.edu*. We’re here to help you transition smoothly into your next chapter.</t>
+          <t>Thank you for your service. The MPA program at SPAA is designed with flexibility and real-world relevance in mind, making it a strong fit for veterans transitioning to civilian public service. Here’s how SPAA supports veterans and aligns with your goals:  
+**Tailored Flexibility**  
+The MPA offers both on-campus and fully online options [link](https://spaa.newark.rutgers.edu/online-mpa), allowing you to balance your studies with personal or professional commitments. The curriculum includes elective courses in areas like nonprofit management, public policy, and leadership, enabling you to customize your degree to reflect your interests or career aspirations in public service [link](https://spaa.newark.rutgers.edu/mpa).  
+**Leadership and Practical Focus**  
+SPAA’s program emphasizes leadership development, a skillset you’ve likely honed through your military experience. The curriculum integrates coursework on managing organizations, ethical challenges, and evidence-based decision-making, preparing you to address complex public sector issues [link](https://spaa.newark.rutgers.edu/mpa). The capstone project allows you to apply your expertise to real-world problems, whether through research or a professional portfolio [link](https://spaa.newark.rutgers.edu/mpa).  
+**Veteran Support and Affordability**  
+SPAA actively supports military-affiliated students, offering resources and infrastructure to help veterans succeed. While the program does not have a specific veteran scholarship, financial aid options—including grants, loans, and tuition assistance—are available to all students [link](https://spaa.newark.rutgers.edu/admissions). Current MPA students also become eligible for SPAA scholarships after completing 9 credits [link](https://spaa.newark.rutgers.edu/online-mpa).  
+**Community and Impact**  
+SPAA’s commitment to public service aligns with your transition to civilian work. The program’s focus on community impact and professional growth ensures you’ll gain the tools to make meaningful contributions in government, nonprofits, or other public-facing roles.  
+If you’re considering applying, the rolling admissions process [link](https://spaa.newark.rutgers.edu/mpa) allows you to submit your application at your convenience, and our team is here to guide you through the next steps.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>batch_test_9e6ea5f6d6b7</t>
+        <v>28.58</v>
+      </c>
+      <c r="E11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>batch_test_77ef16622da24cc2a2e65d508322e653</t>
         </is>
       </c>
     </row>
